--- a/public/templates/expense_report_template.xlsx
+++ b/public/templates/expense_report_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hominseok/업무폴더/영수증마감/26년01월/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hominseok/업무폴더/영수증마감/26년02월/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E99F98-916D-774F-94E9-B393521F1FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6E3DDC-8028-3F48-AF98-F95B480CD8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="600" windowWidth="19200" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="작성법" sheetId="8" state="hidden" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'개인경비 지급요청서'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'법인 지출내역서'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'법인 지출내역서'!$A$1:$H$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="151">
   <si>
     <t>BU 사업부</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -605,144 +605,117 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>품명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(  2  )월 지출 합계 내역</t>
+  </si>
+  <si>
+    <t>4140-0326-9330-7957</t>
+  </si>
+  <si>
+    <t>충전</t>
+  </si>
+  <si>
+    <t>(사)한국자동차환경협</t>
+  </si>
+  <si>
+    <t>석호민</t>
+  </si>
+  <si>
     <t>주유비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>품명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카드번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지에스칼텍스(주)가든</t>
+  </si>
+  <si>
+    <t>주유</t>
+  </si>
+  <si>
+    <t>자동차 관련</t>
   </si>
   <si>
     <t>접대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>식대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>휘발유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>석호민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>석호민/메리츠정태영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>석호민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4140-0326-9330-7957</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고향옥얼큰순대국 문</t>
+  </si>
+  <si>
+    <t>식사</t>
+  </si>
+  <si>
+    <t>사무용품</t>
+  </si>
+  <si>
+    <t>문정동현대지식산업센</t>
+  </si>
+  <si>
+    <t>사무실 임대료</t>
+  </si>
+  <si>
+    <t>택배비</t>
+  </si>
+  <si>
+    <t>우정사업본부(우체국)</t>
+  </si>
+  <si>
+    <t>우편요금</t>
+  </si>
+  <si>
+    <t>플러그링크 전기차충</t>
+  </si>
+  <si>
+    <t>전기차 충전</t>
+  </si>
+  <si>
+    <t>지에스차지비 주식회사</t>
+  </si>
+  <si>
+    <t>삼성전자서비스(주)</t>
   </si>
   <si>
     <t>교통비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>외근식대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지에스칼텍스(주)가든</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연탄고추장삼겹살</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카카오T일반택시_0</t>
+  </si>
+  <si>
+    <t>더벤티 문정점</t>
+  </si>
+  <si>
+    <t>카카오T택시_가승인</t>
+  </si>
+  <si>
+    <t>SK일렉링크</t>
+  </si>
+  <si>
+    <t>서하남아이씨주유소</t>
+  </si>
+  <si>
+    <t>에스케이일렉링크</t>
+  </si>
+  <si>
+    <t>슬비네시골밥상</t>
+  </si>
+  <si>
+    <t>택배</t>
+  </si>
+  <si>
+    <t>형제주유소</t>
   </si>
   <si>
     <t>주차비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아마노코리아(주) 수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메리츠캐피탈 정태영/석호민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>역전할머니맥주 화서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지원스테이션</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배부장찌개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(사)한국자동차환경협</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국전자금융(주)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수원왕족발순대국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>씨앤에스유통(주)내</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지에스차지비 주식회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>삼동소바</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>야근식대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>문정동현대지식산업센</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부리나케</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카카오_택시9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생선구이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(  1  )월 지출 합계 내역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>서울판지</t>
   </si>
 </sst>
 </file>
@@ -1599,21 +1572,30 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1658,15 +1640,6 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2477,7 +2450,7 @@
       </c>
       <c r="B6" s="10">
         <f ca="1">TODAY()</f>
-        <v>46058</v>
+        <v>46086</v>
       </c>
       <c r="C6" s="82" t="s">
         <v>12</v>
@@ -2841,7 +2814,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="73" customWidth="1"/>
@@ -2868,7 +2841,7 @@
     </row>
     <row r="2" spans="1:8" ht="21" customHeight="1">
       <c r="A2" s="83" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -2876,8 +2849,8 @@
       <c r="E2" s="83"/>
       <c r="F2" s="83"/>
       <c r="G2" s="84">
-        <f>SUM(G5:G34)</f>
-        <v>1208513</v>
+        <f>SUM(G5:G41)</f>
+        <v>760285</v>
       </c>
       <c r="H2" s="84"/>
     </row>
@@ -2898,7 +2871,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="65" t="s">
         <v>112</v>
@@ -2907,7 +2880,7 @@
         <v>111</v>
       </c>
       <c r="E4" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>80</v>
@@ -2921,634 +2894,628 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="74">
-        <v>46024</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="64" t="s">
         <v>119</v>
       </c>
+      <c r="E5" s="64"/>
       <c r="F5" s="59" t="s">
         <v>120</v>
       </c>
       <c r="G5" s="66">
-        <v>100000</v>
+        <v>12096</v>
       </c>
       <c r="H5" s="72"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="74">
-        <v>46028</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>129</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="E6" s="64"/>
       <c r="F6" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G6" s="66">
-        <v>1500</v>
+        <v>23658</v>
       </c>
       <c r="H6" s="72"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="74">
-        <v>46028</v>
+        <v>46056</v>
       </c>
       <c r="B7" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="64" t="s">
         <v>119</v>
       </c>
+      <c r="E7" s="64"/>
       <c r="F7" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G7" s="66">
-        <v>90000</v>
+        <v>22607</v>
       </c>
       <c r="H7" s="72"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="74">
-        <v>46028</v>
+        <v>46057</v>
       </c>
       <c r="B8" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="64" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>117</v>
-      </c>
       <c r="F8" s="59" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="G8" s="66">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="H8" s="72"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="74">
-        <v>46028</v>
+        <v>46057</v>
       </c>
       <c r="B9" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E9" s="64" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="G9" s="66">
-        <v>16000</v>
+        <v>22607</v>
       </c>
       <c r="H9" s="72"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="74">
-        <v>46029</v>
+        <v>46059</v>
       </c>
       <c r="B10" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G10" s="66">
-        <v>16117</v>
+        <v>36000</v>
       </c>
       <c r="H10" s="72"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="74">
-        <v>46029</v>
+        <v>46059</v>
       </c>
       <c r="B11" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E11" s="64" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G11" s="66">
-        <v>90000</v>
+        <v>20000</v>
       </c>
       <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="74">
-        <v>46031</v>
+        <v>46060</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="G12" s="66">
-        <v>97000</v>
+        <v>15295</v>
       </c>
       <c r="H12" s="72"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="74">
-        <v>46032</v>
+        <v>46061</v>
       </c>
       <c r="B13" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="64" t="s">
-        <v>135</v>
-      </c>
       <c r="F13" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G13" s="66">
-        <v>1330</v>
+        <v>100000</v>
       </c>
       <c r="H13" s="72"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="74">
-        <v>46033</v>
+        <v>46062</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="64" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G14" s="66">
-        <v>10000</v>
+        <v>3920</v>
       </c>
       <c r="H14" s="72"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="74">
-        <v>46033</v>
+        <v>46062</v>
       </c>
       <c r="B15" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D15" s="64" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E15" s="64" t="s">
         <v>135</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G15" s="66">
-        <v>15125</v>
+        <v>118</v>
       </c>
       <c r="H15" s="72"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="74">
-        <v>46034</v>
+        <v>46063</v>
       </c>
       <c r="B16" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E16" s="64" t="s">
         <v>119</v>
       </c>
       <c r="F16" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G16" s="66">
-        <v>70000</v>
+        <v>7588</v>
       </c>
       <c r="H16" s="72"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="74">
-        <v>46037</v>
+        <v>46063</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E17" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G17" s="66">
-        <v>9886</v>
+        <v>5000</v>
       </c>
       <c r="H17" s="72"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="74">
-        <v>46037</v>
+        <v>46063</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D18" s="64" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E18" s="64" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G18" s="66">
-        <v>68000</v>
+        <v>13442</v>
       </c>
       <c r="H18" s="72"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="74">
-        <v>46038</v>
+        <v>46063</v>
       </c>
       <c r="B19" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D19" s="64" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E19" s="64" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F19" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G19" s="66">
-        <v>80000</v>
+        <v>19000</v>
       </c>
       <c r="H19" s="72"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="74">
-        <v>46039</v>
+        <v>46064</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E20" s="64" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="F20" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G20" s="66">
-        <v>100000</v>
+        <v>33000</v>
       </c>
       <c r="H20" s="72"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="74">
-        <v>46039</v>
+        <v>46064</v>
       </c>
       <c r="B21" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D21" s="64" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21" s="64" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F21" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G21" s="66">
-        <v>8095</v>
+        <v>28400</v>
       </c>
       <c r="H21" s="72"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="74">
-        <v>46039</v>
+        <v>46064</v>
       </c>
       <c r="B22" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D22" s="64" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22" s="64" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G22" s="66">
-        <v>45000</v>
+        <v>-17000</v>
       </c>
       <c r="H22" s="72"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="74">
-        <v>46042</v>
+        <v>46065</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D23" s="64" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E23" s="64" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F23" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G23" s="66">
-        <v>4782</v>
+        <v>90000</v>
       </c>
       <c r="H23" s="72"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="74">
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="B24" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D24" s="64" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="E24" s="64" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="F24" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G24" s="66">
-        <v>10000</v>
+        <v>3494</v>
       </c>
       <c r="H24" s="72"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="74">
-        <v>46045</v>
+        <v>46066</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F25" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G25" s="66">
-        <v>25497</v>
+        <v>5456</v>
       </c>
       <c r="H25" s="72"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="74">
-        <v>46046</v>
+        <v>46069</v>
       </c>
       <c r="B26" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D26" s="64" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E26" s="64" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F26" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G26" s="66">
-        <v>8000</v>
+        <v>-40000</v>
       </c>
       <c r="H26" s="72"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="74">
-        <v>46046</v>
+        <v>46070</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D27" s="64" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E27" s="64" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F27" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G27" s="66">
-        <v>23709</v>
+        <v>4652</v>
       </c>
       <c r="H27" s="72"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="74">
-        <v>46046</v>
+        <v>46070</v>
       </c>
       <c r="B28" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D28" s="64" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E28" s="64" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G28" s="66">
-        <v>6534</v>
+        <v>90000</v>
       </c>
       <c r="H28" s="72"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="74">
-        <v>46047</v>
+        <v>46070</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D29" s="64" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E29" s="64" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F29" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G29" s="66">
-        <v>4638</v>
+        <v>11081</v>
       </c>
       <c r="H29" s="72"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="74">
-        <v>46049</v>
+        <v>46070</v>
       </c>
       <c r="B30" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="E30" s="64" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="F30" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G30" s="66">
-        <v>90000</v>
+        <v>-40000</v>
       </c>
       <c r="H30" s="72"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="74">
-        <v>46050</v>
+        <v>46074</v>
       </c>
       <c r="B31" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C31" s="64" t="s">
         <v>125</v>
@@ -3557,87 +3524,255 @@
         <v>145</v>
       </c>
       <c r="E31" s="64" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="F31" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G31" s="66">
-        <v>50000</v>
+        <v>33000</v>
       </c>
       <c r="H31" s="72"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="74">
-        <v>46050</v>
+        <v>46074</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D32" s="64" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="E32" s="64" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G32" s="66">
-        <v>30300</v>
+        <v>-1000</v>
       </c>
       <c r="H32" s="72"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="74">
-        <v>46050</v>
+        <v>46074</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D33" s="64" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="E33" s="64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F33" s="59" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G33" s="66">
-        <v>42000</v>
+        <v>2720</v>
       </c>
       <c r="H33" s="72"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="74">
-        <v>46052</v>
+        <v>46074</v>
       </c>
       <c r="B34" s="70" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C34" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="66">
+        <v>6644</v>
+      </c>
+      <c r="H34" s="72"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="74">
+        <v>46076</v>
+      </c>
+      <c r="B35" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="66">
+        <v>7850</v>
+      </c>
+      <c r="H35" s="72"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="74">
+        <v>46076</v>
+      </c>
+      <c r="B36" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="66">
+        <v>23300</v>
+      </c>
+      <c r="H36" s="72"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="74">
+        <v>46078</v>
+      </c>
+      <c r="B37" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" s="66">
+        <v>4000</v>
+      </c>
+      <c r="H37" s="72"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="74">
+        <v>46078</v>
+      </c>
+      <c r="B38" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="66">
+        <v>100000</v>
+      </c>
+      <c r="H38" s="72"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="74">
+        <v>46078</v>
+      </c>
+      <c r="B39" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G39" s="66">
+        <v>11000</v>
+      </c>
+      <c r="H39" s="72"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="74">
+        <v>46078</v>
+      </c>
+      <c r="B40" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="64" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="64" t="s">
+      <c r="D40" s="64" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" s="66">
+        <v>800</v>
+      </c>
+      <c r="H40" s="72"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="74">
+        <v>46081</v>
+      </c>
+      <c r="B41" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="F34" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="66">
-        <v>20000</v>
-      </c>
-      <c r="H34" s="72"/>
+      <c r="E41" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41" s="66">
+        <v>11557</v>
+      </c>
+      <c r="H41" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3715,7 +3850,7 @@
         <v>111</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>80</v>
@@ -4121,14 +4256,14 @@
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" ht="30">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -4147,32 +4282,32 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="94" t="s">
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="95"/>
+      <c r="I4" s="99"/>
     </row>
     <row r="5" spans="1:9" ht="18">
-      <c r="A5" s="101"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="111"/>
+      <c r="A5" s="104"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="114"/>
       <c r="H5" s="54" t="s">
         <v>98</v>
       </c>
@@ -4181,8 +4316,8 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="102"/>
-      <c r="B6" s="105"/>
+      <c r="A6" s="105"/>
+      <c r="B6" s="108"/>
       <c r="C6" s="43" t="s">
         <v>3</v>
       </c>
@@ -4198,10 +4333,10 @@
       <c r="G6" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="96" t="s">
+      <c r="H6" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="97"/>
+      <c r="I6" s="101"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="34" t="s">
@@ -4210,13 +4345,13 @@
       <c r="B7" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
       <c r="H7" s="37" t="s">
         <v>39</v>
       </c>
@@ -4231,13 +4366,13 @@
       <c r="B8" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="112" t="s">
+      <c r="C8" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
       <c r="H8" s="39" t="s">
         <v>42</v>
       </c>
@@ -4252,13 +4387,13 @@
       <c r="B9" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
       <c r="H9" s="39" t="s">
         <v>45</v>
       </c>
@@ -4273,13 +4408,13 @@
       <c r="B10" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="C10" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
       <c r="H10" s="40"/>
       <c r="I10" s="41"/>
     </row>
@@ -4295,81 +4430,81 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="98" t="s">
+      <c r="A12" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="98" t="s">
+      <c r="A13" s="95" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="98" t="s">
+      <c r="A14" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="96" t="s">
         <v>91</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="116" t="s">
+      <c r="C17" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="116"/>
+      <c r="D17" s="97"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -4377,14 +4512,14 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="115"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="116" t="s">
+      <c r="C18" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="116"/>
+      <c r="D18" s="97"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -4392,14 +4527,14 @@
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="115"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="116" t="s">
+      <c r="C19" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="116"/>
+      <c r="D19" s="97"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -4407,14 +4542,14 @@
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="115"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="116" t="s">
+      <c r="C20" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="116"/>
+      <c r="D20" s="97"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -4433,10 +4568,10 @@
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="114" t="s">
+      <c r="A22" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="114"/>
+      <c r="B22" s="94"/>
       <c r="C22" s="53" t="s">
         <v>94</v>
       </c>
@@ -4454,10 +4589,10 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="114" t="s">
+      <c r="A23" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="114"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="61"/>
       <c r="D23" s="51"/>
       <c r="E23" s="51"/>
@@ -4491,10 +4626,10 @@
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="94" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="114"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="53" t="s">
         <v>94</v>
       </c>
@@ -4514,10 +4649,10 @@
       <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="114" t="s">
+      <c r="A27" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="114"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="61"/>
       <c r="D27" s="51"/>
       <c r="E27" s="51"/>
@@ -4552,6 +4687,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:G5"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A26:B26"/>
@@ -4564,18 +4711,6 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:G5"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
